--- a/Накладная_2026-07-06.xlsx
+++ b/Накладная_2026-07-06.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <t xml:space="preserve">Унифицированная форма № ТОРГ-12</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t xml:space="preserve">111222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
     <t xml:space="preserve">Но- мер по по- рядку</t>
@@ -347,10 +344,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -770,7 +768,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -846,11 +844,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -870,11 +868,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,7 +940,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2503,8 +2501,8 @@
       <c r="BF26" s="27"/>
       <c r="BG26" s="27"/>
       <c r="BH26" s="27"/>
-      <c r="BI26" s="28" t="s">
-        <v>27</v>
+      <c r="BI26" s="28" t="n">
+        <v>46203</v>
       </c>
       <c r="BJ26" s="28"/>
       <c r="BK26" s="28"/>
@@ -2520,12 +2518,12 @@
     <row r="27" s="14" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" s="33" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
       <c r="D28" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
@@ -2547,7 +2545,7 @@
       <c r="V28" s="30"/>
       <c r="W28" s="30"/>
       <c r="X28" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y28" s="31"/>
       <c r="Z28" s="31"/>
@@ -2559,14 +2557,14 @@
       <c r="AF28" s="31"/>
       <c r="AG28" s="31"/>
       <c r="AH28" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AI28" s="32"/>
       <c r="AJ28" s="32"/>
       <c r="AK28" s="32"/>
       <c r="AL28" s="32"/>
       <c r="AM28" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AN28" s="32"/>
       <c r="AO28" s="32"/>
@@ -2578,14 +2576,14 @@
       <c r="AU28" s="32"/>
       <c r="AV28" s="32"/>
       <c r="AW28" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AX28" s="32"/>
       <c r="AY28" s="32"/>
       <c r="AZ28" s="32"/>
       <c r="BA28" s="32"/>
       <c r="BB28" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BC28" s="32"/>
       <c r="BD28" s="32"/>
@@ -2593,7 +2591,7 @@
       <c r="BF28" s="32"/>
       <c r="BG28" s="32"/>
       <c r="BH28" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BI28" s="32"/>
       <c r="BJ28" s="32"/>
@@ -2604,7 +2602,7 @@
       <c r="BO28" s="32"/>
       <c r="BP28" s="32"/>
       <c r="BQ28" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BR28" s="32"/>
       <c r="BS28" s="32"/>
@@ -2613,7 +2611,7 @@
       <c r="BV28" s="32"/>
       <c r="BW28" s="32"/>
       <c r="BX28" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="BY28" s="32"/>
       <c r="BZ28" s="32"/>
@@ -2626,7 +2624,7 @@
       <c r="CG28" s="32"/>
       <c r="CH28" s="32"/>
       <c r="CI28" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="CJ28" s="32"/>
       <c r="CK28" s="32"/>
@@ -2642,7 +2640,7 @@
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
       <c r="D29" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="32"/>
@@ -2660,20 +2658,20 @@
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U29" s="30"/>
       <c r="V29" s="30"/>
       <c r="W29" s="30"/>
       <c r="X29" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y29" s="32"/>
       <c r="Z29" s="32"/>
       <c r="AA29" s="32"/>
       <c r="AB29" s="32"/>
       <c r="AC29" s="34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD29" s="34"/>
       <c r="AE29" s="34"/>
@@ -2685,14 +2683,14 @@
       <c r="AK29" s="32"/>
       <c r="AL29" s="32"/>
       <c r="AM29" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AN29" s="32"/>
       <c r="AO29" s="32"/>
       <c r="AP29" s="32"/>
       <c r="AQ29" s="32"/>
       <c r="AR29" s="32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AS29" s="32"/>
       <c r="AT29" s="32"/>
@@ -2726,13 +2724,13 @@
       <c r="BV29" s="32"/>
       <c r="BW29" s="32"/>
       <c r="BX29" s="35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="BY29" s="35"/>
       <c r="BZ29" s="35"/>
       <c r="CA29" s="35"/>
       <c r="CB29" s="35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="CC29" s="35"/>
       <c r="CD29" s="35"/>
@@ -2879,12 +2877,12 @@
     </row>
     <row r="31" s="49" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" s="39"/>
       <c r="C31" s="39"/>
       <c r="D31" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" s="40"/>
       <c r="F31" s="40"/>
@@ -2902,27 +2900,27 @@
       <c r="R31" s="40"/>
       <c r="S31" s="40"/>
       <c r="T31" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U31" s="41"/>
       <c r="V31" s="41"/>
       <c r="W31" s="41"/>
       <c r="X31" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y31" s="42"/>
       <c r="Z31" s="42"/>
       <c r="AA31" s="42"/>
       <c r="AB31" s="42"/>
       <c r="AC31" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AD31" s="43"/>
       <c r="AE31" s="43"/>
       <c r="AF31" s="43"/>
       <c r="AG31" s="43"/>
       <c r="AH31" s="44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI31" s="44"/>
       <c r="AJ31" s="44"/>
@@ -2943,7 +2941,7 @@
       <c r="AU31" s="44"/>
       <c r="AV31" s="44"/>
       <c r="AW31" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX31" s="44"/>
       <c r="AY31" s="44"/>
@@ -3008,12 +3006,12 @@
     </row>
     <row r="32" s="49" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="39"/>
       <c r="C32" s="39"/>
       <c r="D32" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" s="40"/>
       <c r="F32" s="40"/>
@@ -3031,27 +3029,27 @@
       <c r="R32" s="40"/>
       <c r="S32" s="40"/>
       <c r="T32" s="50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U32" s="50"/>
       <c r="V32" s="50"/>
       <c r="W32" s="50"/>
       <c r="X32" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y32" s="42"/>
       <c r="Z32" s="42"/>
       <c r="AA32" s="42"/>
       <c r="AB32" s="42"/>
       <c r="AC32" s="51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AD32" s="51"/>
       <c r="AE32" s="51"/>
       <c r="AF32" s="51"/>
       <c r="AG32" s="51"/>
       <c r="AH32" s="52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI32" s="52"/>
       <c r="AJ32" s="52"/>
@@ -3072,7 +3070,7 @@
       <c r="AU32" s="52"/>
       <c r="AV32" s="52"/>
       <c r="AW32" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX32" s="52"/>
       <c r="AY32" s="52"/>
@@ -3138,12 +3136,12 @@
     </row>
     <row r="33" s="49" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" s="39"/>
       <c r="C33" s="39"/>
       <c r="D33" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="40"/>
@@ -3161,27 +3159,27 @@
       <c r="R33" s="40"/>
       <c r="S33" s="40"/>
       <c r="T33" s="50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U33" s="50"/>
       <c r="V33" s="50"/>
       <c r="W33" s="50"/>
       <c r="X33" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y33" s="42"/>
       <c r="Z33" s="42"/>
       <c r="AA33" s="42"/>
       <c r="AB33" s="42"/>
       <c r="AC33" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AD33" s="51"/>
       <c r="AE33" s="51"/>
       <c r="AF33" s="51"/>
       <c r="AG33" s="51"/>
       <c r="AH33" s="52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI33" s="52"/>
       <c r="AJ33" s="52"/>
@@ -3202,7 +3200,7 @@
       <c r="AU33" s="52"/>
       <c r="AV33" s="52"/>
       <c r="AW33" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX33" s="52"/>
       <c r="AY33" s="52"/>
@@ -3267,12 +3265,12 @@
     </row>
     <row r="34" s="49" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" s="39"/>
       <c r="C34" s="39"/>
       <c r="D34" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E34" s="40"/>
       <c r="F34" s="40"/>
@@ -3290,27 +3288,27 @@
       <c r="R34" s="40"/>
       <c r="S34" s="40"/>
       <c r="T34" s="50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U34" s="50"/>
       <c r="V34" s="50"/>
       <c r="W34" s="50"/>
       <c r="X34" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y34" s="42"/>
       <c r="Z34" s="42"/>
       <c r="AA34" s="42"/>
       <c r="AB34" s="42"/>
       <c r="AC34" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AD34" s="51"/>
       <c r="AE34" s="51"/>
       <c r="AF34" s="51"/>
       <c r="AG34" s="51"/>
       <c r="AH34" s="52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI34" s="52"/>
       <c r="AJ34" s="52"/>
@@ -3331,7 +3329,7 @@
       <c r="AU34" s="52"/>
       <c r="AV34" s="52"/>
       <c r="AW34" s="52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX34" s="52"/>
       <c r="AY34" s="52"/>
@@ -3396,12 +3394,12 @@
     </row>
     <row r="35" s="49" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="39"/>
       <c r="C35" s="39"/>
       <c r="D35" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E35" s="40"/>
       <c r="F35" s="40"/>
@@ -3419,27 +3417,27 @@
       <c r="R35" s="40"/>
       <c r="S35" s="40"/>
       <c r="T35" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U35" s="50"/>
       <c r="V35" s="50"/>
       <c r="W35" s="50"/>
       <c r="X35" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y35" s="42"/>
       <c r="Z35" s="42"/>
       <c r="AA35" s="42"/>
       <c r="AB35" s="42"/>
       <c r="AC35" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AD35" s="51"/>
       <c r="AE35" s="51"/>
       <c r="AF35" s="51"/>
       <c r="AG35" s="51"/>
       <c r="AH35" s="52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI35" s="52"/>
       <c r="AJ35" s="52"/>
@@ -3460,7 +3458,7 @@
       <c r="AU35" s="52"/>
       <c r="AV35" s="52"/>
       <c r="AW35" s="52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AX35" s="52"/>
       <c r="AY35" s="52"/>
@@ -4145,7 +4143,7 @@
       <c r="AK42" s="69"/>
       <c r="AL42" s="69"/>
       <c r="AM42" s="70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AN42" s="70"/>
       <c r="AO42" s="70"/>
@@ -4177,7 +4175,7 @@
       <c r="BF42" s="71"/>
       <c r="BG42" s="71"/>
       <c r="BH42" s="72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BI42" s="72"/>
       <c r="BJ42" s="72"/>
@@ -4198,7 +4196,7 @@
       <c r="BV42" s="71"/>
       <c r="BW42" s="71"/>
       <c r="BX42" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BY42" s="36"/>
       <c r="BZ42" s="36"/>
@@ -4228,7 +4226,7 @@
     </row>
     <row r="43" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AQ43" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AR43" s="71" t="n">
         <f aca="false">AR42</f>
@@ -4256,7 +4254,7 @@
       <c r="BF43" s="71"/>
       <c r="BG43" s="71"/>
       <c r="BH43" s="72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BI43" s="72"/>
       <c r="BJ43" s="72"/>
@@ -4277,7 +4275,7 @@
       <c r="BV43" s="71"/>
       <c r="BW43" s="71"/>
       <c r="BX43" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="BY43" s="36"/>
       <c r="BZ43" s="36"/>
@@ -4308,7 +4306,7 @@
     <row r="44" s="14" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="45" s="73" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="73" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Y45" s="74" t="n">
         <v>1</v>
@@ -4355,15 +4353,15 @@
       <c r="BM45" s="74"/>
       <c r="BN45" s="74"/>
       <c r="BO45" s="73" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" s="73" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D46" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="O46" s="74" t="s">
         <v>76</v>
-      </c>
-      <c r="O46" s="74" t="s">
-        <v>77</v>
       </c>
       <c r="P46" s="74"/>
       <c r="Q46" s="74"/>
@@ -4417,12 +4415,12 @@
       <c r="BM46" s="74"/>
       <c r="BN46" s="74"/>
       <c r="BO46" s="73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" s="73" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="O47" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -4551,10 +4549,10 @@
     </row>
     <row r="50" s="73" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AC50" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN50" s="74" t="s">
         <v>80</v>
-      </c>
-      <c r="AN50" s="74" t="s">
-        <v>81</v>
       </c>
       <c r="AO50" s="74"/>
       <c r="AP50" s="74"/>
@@ -4613,7 +4611,7 @@
     </row>
     <row r="51" s="73" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AN51" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO51" s="9"/>
       <c r="AP51" s="9"/>
@@ -4672,10 +4670,10 @@
     </row>
     <row r="52" s="73" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K52" s="74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L52" s="74"/>
       <c r="M52" s="74"/>
@@ -4695,10 +4693,10 @@
       <c r="AA52" s="74"/>
       <c r="AB52" s="78"/>
       <c r="AC52" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN52" s="74" t="s">
         <v>83</v>
-      </c>
-      <c r="AN52" s="74" t="s">
-        <v>84</v>
       </c>
       <c r="AO52" s="74"/>
       <c r="AP52" s="74"/>
@@ -4757,7 +4755,7 @@
     </row>
     <row r="53" s="73" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K53" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
@@ -4777,7 +4775,7 @@
       <c r="AA53" s="9"/>
       <c r="AB53" s="75"/>
       <c r="AN53" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AO53" s="9"/>
       <c r="AP53" s="9"/>
@@ -4820,7 +4818,7 @@
     <row r="54" s="73" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="55" s="79" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X55" s="80"/>
       <c r="Y55" s="80"/>
@@ -4843,11 +4841,11 @@
       <c r="AP55" s="80"/>
       <c r="AQ55" s="80"/>
       <c r="AS55" s="79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AV55" s="81"/>
       <c r="AY55" s="79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BI55" s="80"/>
       <c r="BJ55" s="80"/>
@@ -4863,12 +4861,12 @@
       <c r="BT55" s="80"/>
       <c r="BU55" s="80"/>
       <c r="BX55" s="82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BY55" s="80"/>
       <c r="BZ55" s="80"/>
       <c r="CA55" s="83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="CC55" s="84"/>
       <c r="CD55" s="84"/>
@@ -4883,14 +4881,14 @@
       <c r="CM55" s="80"/>
       <c r="CN55" s="80"/>
       <c r="CO55" s="85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="CP55" s="85"/>
       <c r="CQ55" s="85"/>
     </row>
     <row r="56" s="79" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="X56" s="86" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y56" s="86"/>
       <c r="Z56" s="86"/>
@@ -4915,7 +4913,7 @@
     </row>
     <row r="57" s="79" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N57" s="80"/>
       <c r="O57" s="80"/>
@@ -4951,7 +4949,7 @@
       <c r="AS57" s="80"/>
       <c r="AV57" s="81"/>
       <c r="AY57" s="79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BE57" s="84"/>
       <c r="BF57" s="84"/>
@@ -4995,11 +4993,11 @@
     </row>
     <row r="58" s="79" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V58" s="87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AV58" s="81"/>
       <c r="BE58" s="86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BF58" s="86"/>
       <c r="BG58" s="86"/>
@@ -5077,7 +5075,7 @@
       <c r="AH59" s="84"/>
       <c r="AI59" s="84"/>
       <c r="AJ59" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AK59" s="85"/>
       <c r="AL59" s="85"/>
@@ -5089,7 +5087,7 @@
       <c r="AR59" s="84"/>
       <c r="AS59" s="84"/>
       <c r="AT59" s="88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU59" s="88"/>
       <c r="AV59" s="88"/>
@@ -5145,7 +5143,7 @@
     </row>
     <row r="61" s="79" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J61" s="80"/>
       <c r="K61" s="80"/>
@@ -5235,7 +5233,7 @@
     </row>
     <row r="62" s="79" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J62" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K62" s="86"/>
       <c r="L62" s="86"/>
@@ -5248,7 +5246,7 @@
       <c r="S62" s="86"/>
       <c r="T62" s="86"/>
       <c r="V62" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W62" s="86"/>
       <c r="X62" s="86"/>
@@ -5261,7 +5259,7 @@
       <c r="AE62" s="86"/>
       <c r="AF62" s="90"/>
       <c r="AG62" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AH62" s="86"/>
       <c r="AI62" s="86"/>
@@ -5281,7 +5279,7 @@
     </row>
     <row r="63" s="79" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="V63" s="80"/>
       <c r="W63" s="80"/>
@@ -5311,7 +5309,7 @@
       <c r="AU63" s="80"/>
       <c r="AV63" s="81"/>
       <c r="AY63" s="79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BF63" s="80"/>
       <c r="BG63" s="80"/>
@@ -5354,7 +5352,7 @@
     </row>
     <row r="64" s="79" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="V64" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W64" s="86"/>
       <c r="X64" s="86"/>
@@ -5366,7 +5364,7 @@
       <c r="AD64" s="86"/>
       <c r="AE64" s="86"/>
       <c r="AG64" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AH64" s="86"/>
       <c r="AI64" s="86"/>
@@ -5384,7 +5382,7 @@
       <c r="AU64" s="86"/>
       <c r="AV64" s="81"/>
       <c r="BF64" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BG64" s="86"/>
       <c r="BH64" s="86"/>
@@ -5396,7 +5394,7 @@
       <c r="BN64" s="86"/>
       <c r="BO64" s="91"/>
       <c r="BP64" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BQ64" s="86"/>
       <c r="BR64" s="86"/>
@@ -5407,7 +5405,7 @@
       <c r="BW64" s="86"/>
       <c r="BX64" s="91"/>
       <c r="BY64" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BZ64" s="86"/>
       <c r="CA64" s="86"/>
@@ -5430,7 +5428,7 @@
     </row>
     <row r="65" s="79" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K65" s="92"/>
       <c r="L65" s="80"/>
@@ -5471,7 +5469,7 @@
       <c r="AU65" s="85"/>
       <c r="AV65" s="81"/>
       <c r="AY65" s="79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO65" s="80"/>
       <c r="BP65" s="80"/>
@@ -5505,7 +5503,7 @@
     </row>
     <row r="66" s="79" customFormat="true" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="L66" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M66" s="86"/>
       <c r="N66" s="86"/>
@@ -5516,7 +5514,7 @@
       <c r="S66" s="86"/>
       <c r="T66" s="86"/>
       <c r="V66" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W66" s="86"/>
       <c r="X66" s="86"/>
@@ -5529,7 +5527,7 @@
       <c r="AE66" s="86"/>
       <c r="AF66" s="90"/>
       <c r="AG66" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AH66" s="86"/>
       <c r="AI66" s="86"/>
@@ -5547,7 +5545,7 @@
       <c r="AU66" s="86"/>
       <c r="AV66" s="81"/>
       <c r="BO66" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BP66" s="86"/>
       <c r="BQ66" s="86"/>
@@ -5559,7 +5557,7 @@
       <c r="BW66" s="86"/>
       <c r="BX66" s="91"/>
       <c r="BY66" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BZ66" s="86"/>
       <c r="CA66" s="86"/>
@@ -5568,7 +5566,7 @@
       <c r="CD66" s="86"/>
       <c r="CE66" s="91"/>
       <c r="CF66" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="CG66" s="86"/>
       <c r="CH66" s="86"/>
@@ -5587,11 +5585,11 @@
     </row>
     <row r="68" s="79" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G68" s="93" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AV68" s="81"/>
       <c r="AY68" s="79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
